--- a/database/event/5553/event_5553_evp_summary.xlsx
+++ b/database/event/5553/event_5553_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>4.3491</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E2" t="n">
         <v>6.4635</v>
@@ -514,7 +514,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>10.7476</v>
+        <v>10.1616</v>
       </c>
       <c r="I2" t="n">
         <v>11.5229</v>
@@ -548,7 +548,7 @@
         <v>4.3491</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E3" t="n">
         <v>6.4635</v>
@@ -560,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>9.4595</v>
+        <v>8.910399999999999</v>
       </c>
       <c r="I3" t="n">
         <v>10.1891</v>
@@ -594,7 +594,7 @@
         <v>4.3491</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E4" t="n">
         <v>6.4635</v>
@@ -606,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>11.1141</v>
+        <v>10.469</v>
       </c>
       <c r="I4" t="n">
         <v>11.9713</v>
@@ -640,7 +640,7 @@
         <v>4.3491</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1897</v>
+        <v>2.1311</v>
       </c>
       <c r="E5" t="n">
         <v>6.4635</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>9.130000000000001</v>
+        <v>8.5679</v>
       </c>
       <c r="I5" t="n">
         <v>9.879899999999999</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.4201</v>
+        <v>6.2029</v>
       </c>
       <c r="C6" t="n">
-        <v>4.3199</v>
+        <v>4.1738</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1722</v>
+        <v>2.0273</v>
       </c>
       <c r="E6" t="n">
-        <v>6.4201</v>
+        <v>6.2029</v>
       </c>
       <c r="F6" t="n">
-        <v>6.4201</v>
+        <v>6.2029</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>7.7636</v>
+        <v>7.4231</v>
       </c>
       <c r="I6" t="n">
         <v>8.208500000000001</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.9291</v>
+        <v>5.7655</v>
       </c>
       <c r="C7" t="n">
-        <v>3.9895</v>
+        <v>3.8794</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9739</v>
+        <v>1.8531</v>
       </c>
       <c r="E7" t="n">
-        <v>5.9291</v>
+        <v>5.7655</v>
       </c>
       <c r="F7" t="n">
-        <v>5.9291</v>
+        <v>5.7655</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>6.9938</v>
+        <v>6.7372</v>
       </c>
       <c r="I7" t="n">
         <v>7.3262</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.7832</v>
+        <v>5.6249</v>
       </c>
       <c r="C8" t="n">
-        <v>3.8914</v>
+        <v>3.7848</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9149</v>
+        <v>1.7971</v>
       </c>
       <c r="E8" t="n">
-        <v>5.7832</v>
+        <v>5.6249</v>
       </c>
       <c r="F8" t="n">
-        <v>5.7832</v>
+        <v>5.6249</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>6.765</v>
+        <v>6.5168</v>
       </c>
       <c r="I8" t="n">
         <v>7.0865</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.6919</v>
+        <v>5.537</v>
       </c>
       <c r="C9" t="n">
-        <v>3.8299</v>
+        <v>3.7257</v>
       </c>
       <c r="D9" t="n">
-        <v>1.878</v>
+        <v>1.762</v>
       </c>
       <c r="E9" t="n">
-        <v>5.6919</v>
+        <v>5.537</v>
       </c>
       <c r="F9" t="n">
-        <v>5.6919</v>
+        <v>5.537</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>6.6219</v>
+        <v>6.379</v>
       </c>
       <c r="I9" t="n">
         <v>6.9366</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.5649</v>
+        <v>5.3852</v>
       </c>
       <c r="C10" t="n">
-        <v>3.7445</v>
+        <v>3.6236</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8267</v>
+        <v>1.7016</v>
       </c>
       <c r="E10" t="n">
-        <v>5.5649</v>
+        <v>5.3852</v>
       </c>
       <c r="F10" t="n">
-        <v>5.5649</v>
+        <v>5.3852</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>6.4227</v>
+        <v>6.141</v>
       </c>
       <c r="I10" t="n">
         <v>6.7907</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.3068</v>
+        <v>5.1522</v>
       </c>
       <c r="C11" t="n">
-        <v>3.5708</v>
+        <v>3.4668</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7225</v>
+        <v>1.6087</v>
       </c>
       <c r="E11" t="n">
-        <v>5.3068</v>
+        <v>5.1522</v>
       </c>
       <c r="F11" t="n">
-        <v>5.3068</v>
+        <v>5.1522</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>6.018</v>
+        <v>5.7756</v>
       </c>
       <c r="I11" t="n">
         <v>6.3334</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.1944</v>
+        <v>5.0443</v>
       </c>
       <c r="C12" t="n">
-        <v>3.4952</v>
+        <v>3.3942</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6771</v>
+        <v>1.5657</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1944</v>
+        <v>5.0443</v>
       </c>
       <c r="F12" t="n">
-        <v>5.1944</v>
+        <v>5.0443</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5.8417</v>
+        <v>5.6064</v>
       </c>
       <c r="I12" t="n">
         <v>6.1479</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.1036</v>
+        <v>4.8799</v>
       </c>
       <c r="C13" t="n">
-        <v>3.4341</v>
+        <v>3.2835</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6404</v>
+        <v>1.5002</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1036</v>
+        <v>4.8799</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1036</v>
+        <v>4.8799</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>5.6994</v>
+        <v>5.3486</v>
       </c>
       <c r="I13" t="n">
         <v>6.1676</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.9254</v>
+        <v>4.811</v>
       </c>
       <c r="C14" t="n">
-        <v>3.3142</v>
+        <v>3.2372</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5684</v>
+        <v>1.4728</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9254</v>
+        <v>4.811</v>
       </c>
       <c r="F14" t="n">
-        <v>4.9254</v>
+        <v>4.811</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4199</v>
+        <v>5.2406</v>
       </c>
       <c r="I14" t="n">
         <v>5.6512</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.9089</v>
+        <v>4.7213</v>
       </c>
       <c r="C15" t="n">
-        <v>3.3031</v>
+        <v>3.1768</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5617</v>
+        <v>1.4371</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9089</v>
+        <v>4.7213</v>
       </c>
       <c r="F15" t="n">
-        <v>4.9089</v>
+        <v>4.7213</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3941</v>
+        <v>5.1</v>
       </c>
       <c r="I15" t="n">
         <v>5.7832</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.8068</v>
+        <v>4.6964</v>
       </c>
       <c r="C16" t="n">
-        <v>3.2344</v>
+        <v>3.1601</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5205</v>
+        <v>1.4271</v>
       </c>
       <c r="E16" t="n">
-        <v>4.8068</v>
+        <v>4.6964</v>
       </c>
       <c r="F16" t="n">
-        <v>4.8068</v>
+        <v>4.6964</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>5.234</v>
+        <v>5.0608</v>
       </c>
       <c r="I16" t="n">
         <v>5.4574</v>
@@ -1182,47 +1182,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.7621</v>
+        <v>4.6292</v>
       </c>
       <c r="C17" t="n">
-        <v>3.2043</v>
+        <v>3.1149</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5024</v>
+        <v>1.4004</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7621</v>
+        <v>4.6292</v>
       </c>
       <c r="F17" t="n">
-        <v>4.7621</v>
+        <v>4.6292</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5.1638</v>
+        <v>4.9555</v>
       </c>
       <c r="I17" t="n">
-        <v>5.588</v>
+        <v>5.1245</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>606</v>
+        <v>282</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>5.588</v>
+        <v>5.1245</v>
       </c>
       <c r="N17" t="n">
-        <v>606</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18">
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.6999</v>
+        <v>4.593</v>
       </c>
       <c r="C18" t="n">
-        <v>3.1624</v>
+        <v>3.0905</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4773</v>
+        <v>1.3859</v>
       </c>
       <c r="E18" t="n">
-        <v>4.6999</v>
+        <v>4.593</v>
       </c>
       <c r="F18" t="n">
-        <v>4.6999</v>
+        <v>4.593</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5.0664</v>
+        <v>4.8988</v>
       </c>
       <c r="I18" t="n">
         <v>5.2826</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.6768</v>
+        <v>4.5593</v>
       </c>
       <c r="C19" t="n">
-        <v>3.1469</v>
+        <v>3.0678</v>
       </c>
       <c r="D19" t="n">
-        <v>1.468</v>
+        <v>1.3725</v>
       </c>
       <c r="E19" t="n">
-        <v>4.6768</v>
+        <v>4.5593</v>
       </c>
       <c r="F19" t="n">
-        <v>4.6768</v>
+        <v>4.5593</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>5.0302</v>
+        <v>4.8459</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1245</v>
+        <v>5.588</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>282</v>
+        <v>606</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1245</v>
+        <v>5.588</v>
       </c>
       <c r="N19" t="n">
-        <v>282</v>
+        <v>606</v>
       </c>
     </row>
     <row r="20">
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.6349</v>
+        <v>4.5187</v>
       </c>
       <c r="C20" t="n">
-        <v>3.1187</v>
+        <v>3.0405</v>
       </c>
       <c r="D20" t="n">
-        <v>1.451</v>
+        <v>1.3563</v>
       </c>
       <c r="E20" t="n">
-        <v>4.6349</v>
+        <v>4.5187</v>
       </c>
       <c r="F20" t="n">
-        <v>4.6349</v>
+        <v>4.5187</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.9644</v>
+        <v>4.7823</v>
       </c>
       <c r="I20" t="n">
         <v>5.2003</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.4722</v>
+        <v>4.3837</v>
       </c>
       <c r="C21" t="n">
-        <v>3.0092</v>
+        <v>2.9497</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3853</v>
+        <v>1.3026</v>
       </c>
       <c r="E21" t="n">
-        <v>4.4722</v>
+        <v>4.3837</v>
       </c>
       <c r="F21" t="n">
-        <v>4.4722</v>
+        <v>4.3837</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7093</v>
+        <v>4.5706</v>
       </c>
       <c r="I21" t="n">
         <v>4.8875</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4.4245</v>
+        <v>4.3806</v>
       </c>
       <c r="C22" t="n">
-        <v>2.9771</v>
+        <v>2.9476</v>
       </c>
       <c r="D22" t="n">
-        <v>1.366</v>
+        <v>1.3013</v>
       </c>
       <c r="E22" t="n">
-        <v>4.4245</v>
+        <v>4.3806</v>
       </c>
       <c r="F22" t="n">
-        <v>4.4245</v>
+        <v>4.3806</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6345</v>
+        <v>4.5657</v>
       </c>
       <c r="I22" t="n">
         <v>4.7214</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.4172</v>
+        <v>4.3196</v>
       </c>
       <c r="C23" t="n">
-        <v>2.9722</v>
+        <v>2.9065</v>
       </c>
       <c r="D23" t="n">
-        <v>1.3631</v>
+        <v>1.277</v>
       </c>
       <c r="E23" t="n">
-        <v>4.4172</v>
+        <v>4.3196</v>
       </c>
       <c r="F23" t="n">
-        <v>4.4172</v>
+        <v>4.3196</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4.623</v>
+        <v>4.4701</v>
       </c>
       <c r="I23" t="n">
         <v>4.8203</v>
@@ -1504,139 +1504,139 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.3738</v>
+        <v>4.3091</v>
       </c>
       <c r="C24" t="n">
-        <v>2.943</v>
+        <v>2.8995</v>
       </c>
       <c r="D24" t="n">
-        <v>1.3456</v>
+        <v>1.2728</v>
       </c>
       <c r="E24" t="n">
-        <v>4.3738</v>
+        <v>4.3091</v>
       </c>
       <c r="F24" t="n">
-        <v>4.3738</v>
+        <v>4.3091</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5551</v>
+        <v>4.4536</v>
       </c>
       <c r="I24" t="n">
-        <v>4.8161</v>
+        <v>4.6442</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>532</v>
+        <v>280</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.8161</v>
+        <v>4.6442</v>
       </c>
       <c r="N24" t="n">
-        <v>532</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.3627</v>
+        <v>4.3026</v>
       </c>
       <c r="C25" t="n">
-        <v>2.9355</v>
+        <v>2.8951</v>
       </c>
       <c r="D25" t="n">
-        <v>1.3411</v>
+        <v>1.2702</v>
       </c>
       <c r="E25" t="n">
-        <v>4.3627</v>
+        <v>4.3026</v>
       </c>
       <c r="F25" t="n">
-        <v>4.3627</v>
+        <v>4.3026</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5376</v>
+        <v>4.4435</v>
       </c>
       <c r="I25" t="n">
-        <v>4.6442</v>
+        <v>4.595</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>280</v>
+        <v>361</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.6442</v>
+        <v>4.595</v>
       </c>
       <c r="N25" t="n">
-        <v>280</v>
+        <v>361</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.3453</v>
+        <v>4.2464</v>
       </c>
       <c r="C26" t="n">
-        <v>2.9238</v>
+        <v>2.8573</v>
       </c>
       <c r="D26" t="n">
-        <v>1.334</v>
+        <v>1.2479</v>
       </c>
       <c r="E26" t="n">
-        <v>4.3453</v>
+        <v>4.2464</v>
       </c>
       <c r="F26" t="n">
-        <v>4.3453</v>
+        <v>4.2464</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4.5104</v>
+        <v>4.3553</v>
       </c>
       <c r="I26" t="n">
-        <v>4.595</v>
+        <v>4.8161</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>361</v>
+        <v>532</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.595</v>
+        <v>4.8161</v>
       </c>
       <c r="N26" t="n">
-        <v>361</v>
+        <v>532</v>
       </c>
     </row>
     <row r="27">
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.3095</v>
+        <v>4.2053</v>
       </c>
       <c r="C27" t="n">
-        <v>2.8997</v>
+        <v>2.8296</v>
       </c>
       <c r="D27" t="n">
-        <v>1.3196</v>
+        <v>1.2315</v>
       </c>
       <c r="E27" t="n">
-        <v>4.3095</v>
+        <v>4.2053</v>
       </c>
       <c r="F27" t="n">
-        <v>4.3095</v>
+        <v>4.2053</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4543</v>
+        <v>4.2909</v>
       </c>
       <c r="I27" t="n">
         <v>4.666</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4.2515</v>
+        <v>4.0802</v>
       </c>
       <c r="C28" t="n">
-        <v>2.8607</v>
+        <v>2.7455</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2961</v>
+        <v>1.1816</v>
       </c>
       <c r="E28" t="n">
-        <v>4.2515</v>
+        <v>4.0802</v>
       </c>
       <c r="F28" t="n">
-        <v>4.2515</v>
+        <v>4.0802</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4.3633</v>
+        <v>4.0946</v>
       </c>
       <c r="I28" t="n">
         <v>4.7217</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4.1611</v>
+        <v>4.0364</v>
       </c>
       <c r="C29" t="n">
-        <v>2.7999</v>
+        <v>2.716</v>
       </c>
       <c r="D29" t="n">
-        <v>1.2596</v>
+        <v>1.1642</v>
       </c>
       <c r="E29" t="n">
-        <v>4.1611</v>
+        <v>4.0364</v>
       </c>
       <c r="F29" t="n">
-        <v>4.1611</v>
+        <v>4.0364</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>4.2216</v>
+        <v>4.0364</v>
       </c>
       <c r="I29" t="n">
         <v>4.4635</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4.0522</v>
+        <v>3.9036</v>
       </c>
       <c r="C30" t="n">
-        <v>2.7266</v>
+        <v>2.6266</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2156</v>
+        <v>1.1113</v>
       </c>
       <c r="E30" t="n">
-        <v>4.0522</v>
+        <v>3.9036</v>
       </c>
       <c r="F30" t="n">
-        <v>4.0522</v>
+        <v>3.9036</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>4.0522</v>
+        <v>3.9036</v>
       </c>
       <c r="I30" t="n">
         <v>4.2448</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.6782</v>
+        <v>3.5566</v>
       </c>
       <c r="C31" t="n">
-        <v>2.475</v>
+        <v>2.3931</v>
       </c>
       <c r="D31" t="n">
-        <v>1.0645</v>
+        <v>0.973</v>
       </c>
       <c r="E31" t="n">
-        <v>3.6782</v>
+        <v>3.5566</v>
       </c>
       <c r="F31" t="n">
-        <v>3.6782</v>
+        <v>3.5566</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3.6782</v>
+        <v>3.5566</v>
       </c>
       <c r="I31" t="n">
         <v>3.8352</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.5711</v>
+        <v>3.453</v>
       </c>
       <c r="C32" t="n">
-        <v>2.4029</v>
+        <v>2.3234</v>
       </c>
       <c r="D32" t="n">
-        <v>1.0213</v>
+        <v>0.9318</v>
       </c>
       <c r="E32" t="n">
-        <v>3.5711</v>
+        <v>3.453</v>
       </c>
       <c r="F32" t="n">
-        <v>3.5711</v>
+        <v>3.453</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3.5711</v>
+        <v>3.453</v>
       </c>
       <c r="I32" t="n">
         <v>3.7235</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3.5289</v>
+        <v>3.4506</v>
       </c>
       <c r="C33" t="n">
-        <v>2.3745</v>
+        <v>2.3218</v>
       </c>
       <c r="D33" t="n">
-        <v>1.0042</v>
+        <v>0.9308</v>
       </c>
       <c r="E33" t="n">
-        <v>3.5289</v>
+        <v>3.4506</v>
       </c>
       <c r="F33" t="n">
-        <v>3.5289</v>
+        <v>3.4506</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3.5289</v>
+        <v>3.4506</v>
       </c>
       <c r="I33" t="n">
         <v>3.6286</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.3839</v>
+        <v>3.3213</v>
       </c>
       <c r="C34" t="n">
-        <v>2.2769</v>
+        <v>2.2348</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9457</v>
+        <v>0.8793</v>
       </c>
       <c r="E34" t="n">
-        <v>3.3839</v>
+        <v>3.3213</v>
       </c>
       <c r="F34" t="n">
-        <v>3.3839</v>
+        <v>3.3213</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.3839</v>
+        <v>3.3213</v>
       </c>
       <c r="I34" t="n">
         <v>3.4634</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.2246</v>
+        <v>3.1531</v>
       </c>
       <c r="C35" t="n">
-        <v>2.1697</v>
+        <v>2.1216</v>
       </c>
       <c r="D35" t="n">
-        <v>0.8813</v>
+        <v>0.8123</v>
       </c>
       <c r="E35" t="n">
-        <v>3.2246</v>
+        <v>3.1531</v>
       </c>
       <c r="F35" t="n">
-        <v>3.2246</v>
+        <v>3.1531</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>3.2246</v>
+        <v>3.1531</v>
       </c>
       <c r="I35" t="n">
         <v>3.3157</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3.1554</v>
+        <v>3.0396</v>
       </c>
       <c r="C36" t="n">
-        <v>2.1232</v>
+        <v>2.0453</v>
       </c>
       <c r="D36" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.7671</v>
       </c>
       <c r="E36" t="n">
-        <v>3.1554</v>
+        <v>3.0396</v>
       </c>
       <c r="F36" t="n">
-        <v>3.1554</v>
+        <v>3.0396</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3.1554</v>
+        <v>3.0396</v>
       </c>
       <c r="I36" t="n">
         <v>3.3053</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.0496</v>
+        <v>2.9488</v>
       </c>
       <c r="C37" t="n">
-        <v>2.052</v>
+        <v>1.9842</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8106</v>
+        <v>0.7309</v>
       </c>
       <c r="E37" t="n">
-        <v>3.0496</v>
+        <v>2.9488</v>
       </c>
       <c r="F37" t="n">
-        <v>3.0496</v>
+        <v>2.9488</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3.0496</v>
+        <v>2.9488</v>
       </c>
       <c r="I37" t="n">
         <v>3.1798</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.0206</v>
+        <v>2.9207</v>
       </c>
       <c r="C38" t="n">
-        <v>2.0325</v>
+        <v>1.9653</v>
       </c>
       <c r="D38" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.7197</v>
       </c>
       <c r="E38" t="n">
-        <v>3.0206</v>
+        <v>2.9207</v>
       </c>
       <c r="F38" t="n">
-        <v>3.0206</v>
+        <v>2.9207</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3.0206</v>
+        <v>2.9207</v>
       </c>
       <c r="I38" t="n">
         <v>3.1496</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.8161</v>
+        <v>2.7536</v>
       </c>
       <c r="C39" t="n">
-        <v>1.8949</v>
+        <v>1.8528</v>
       </c>
       <c r="D39" t="n">
-        <v>0.7163</v>
+        <v>0.6531</v>
       </c>
       <c r="E39" t="n">
-        <v>2.8161</v>
+        <v>2.7536</v>
       </c>
       <c r="F39" t="n">
-        <v>2.8161</v>
+        <v>2.7536</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.8161</v>
+        <v>2.7536</v>
       </c>
       <c r="I39" t="n">
         <v>2.8956</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.5672</v>
+        <v>2.5291</v>
       </c>
       <c r="C40" t="n">
-        <v>1.7274</v>
+        <v>1.7018</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6157</v>
+        <v>0.5637</v>
       </c>
       <c r="E40" t="n">
-        <v>2.5672</v>
+        <v>2.5291</v>
       </c>
       <c r="F40" t="n">
-        <v>2.5672</v>
+        <v>2.5291</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2.5672</v>
+        <v>2.5291</v>
       </c>
       <c r="I40" t="n">
         <v>2.6153</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.5427</v>
+        <v>2.4586</v>
       </c>
       <c r="C41" t="n">
-        <v>1.7109</v>
+        <v>1.6543</v>
       </c>
       <c r="D41" t="n">
-        <v>0.6058</v>
+        <v>0.5356</v>
       </c>
       <c r="E41" t="n">
-        <v>2.5427</v>
+        <v>2.4586</v>
       </c>
       <c r="F41" t="n">
-        <v>2.5427</v>
+        <v>2.4586</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2.5427</v>
+        <v>2.4586</v>
       </c>
       <c r="I41" t="n">
         <v>2.6512</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.3886</v>
+        <v>2.3532</v>
       </c>
       <c r="C42" t="n">
-        <v>1.6072</v>
+        <v>1.5834</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5436</v>
+        <v>0.4936</v>
       </c>
       <c r="E42" t="n">
-        <v>2.3886</v>
+        <v>2.3532</v>
       </c>
       <c r="F42" t="n">
-        <v>2.3886</v>
+        <v>2.3532</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.3886</v>
+        <v>2.3532</v>
       </c>
       <c r="I42" t="n">
         <v>2.4334</v>
@@ -2378,93 +2378,93 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.2844</v>
+        <v>2.2432</v>
       </c>
       <c r="C43" t="n">
-        <v>1.5371</v>
+        <v>1.5094</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4498</v>
       </c>
       <c r="E43" t="n">
-        <v>2.2844</v>
+        <v>2.2432</v>
       </c>
       <c r="F43" t="n">
-        <v>2.2844</v>
+        <v>2.2432</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2.2844</v>
+        <v>2.2432</v>
       </c>
       <c r="I43" t="n">
-        <v>2.3381</v>
+        <v>2.2811</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.3381</v>
+        <v>2.2811</v>
       </c>
       <c r="N43" t="n">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.26</v>
+        <v>2.2421</v>
       </c>
       <c r="C44" t="n">
-        <v>1.5207</v>
+        <v>1.5086</v>
       </c>
       <c r="D44" t="n">
-        <v>0.4916</v>
+        <v>0.4493</v>
       </c>
       <c r="E44" t="n">
-        <v>2.26</v>
+        <v>2.2421</v>
       </c>
       <c r="F44" t="n">
-        <v>2.26</v>
+        <v>2.2421</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>2.26</v>
+        <v>2.2421</v>
       </c>
       <c r="I44" t="n">
-        <v>2.2811</v>
+        <v>2.3381</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.2811</v>
+        <v>2.3381</v>
       </c>
       <c r="N44" t="n">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="45">
@@ -2474,25 +2474,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.0817</v>
+        <v>2.0508</v>
       </c>
       <c r="C45" t="n">
-        <v>1.4007</v>
+        <v>1.3799</v>
       </c>
       <c r="D45" t="n">
-        <v>0.4196</v>
+        <v>0.3731</v>
       </c>
       <c r="E45" t="n">
-        <v>2.0817</v>
+        <v>2.0508</v>
       </c>
       <c r="F45" t="n">
-        <v>2.0817</v>
+        <v>2.0508</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>2.0817</v>
+        <v>2.0508</v>
       </c>
       <c r="I45" t="n">
         <v>2.1207</v>
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.9946</v>
+        <v>1.965</v>
       </c>
       <c r="C46" t="n">
-        <v>1.3421</v>
+        <v>1.3222</v>
       </c>
       <c r="D46" t="n">
-        <v>0.3844</v>
+        <v>0.3389</v>
       </c>
       <c r="E46" t="n">
-        <v>1.9946</v>
+        <v>1.965</v>
       </c>
       <c r="F46" t="n">
-        <v>1.9946</v>
+        <v>1.965</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.9946</v>
+        <v>1.965</v>
       </c>
       <c r="I46" t="n">
         <v>2.032</v>
@@ -2566,25 +2566,25 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.9585</v>
+        <v>1.9222</v>
       </c>
       <c r="C47" t="n">
-        <v>1.3178</v>
+        <v>1.2934</v>
       </c>
       <c r="D47" t="n">
-        <v>0.3698</v>
+        <v>0.3219</v>
       </c>
       <c r="E47" t="n">
-        <v>1.9585</v>
+        <v>1.9222</v>
       </c>
       <c r="F47" t="n">
-        <v>1.9585</v>
+        <v>1.9222</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.9585</v>
+        <v>1.9222</v>
       </c>
       <c r="I47" t="n">
         <v>2.0045</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.8997</v>
+        <v>1.8645</v>
       </c>
       <c r="C48" t="n">
-        <v>1.2783</v>
+        <v>1.2546</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3461</v>
+        <v>0.2989</v>
       </c>
       <c r="E48" t="n">
-        <v>1.8997</v>
+        <v>1.8645</v>
       </c>
       <c r="F48" t="n">
-        <v>1.8997</v>
+        <v>1.8645</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.8997</v>
+        <v>1.8645</v>
       </c>
       <c r="I48" t="n">
         <v>1.9443</v>
@@ -2658,25 +2658,25 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.7914</v>
+        <v>1.7648</v>
       </c>
       <c r="C49" t="n">
-        <v>1.2054</v>
+        <v>1.1875</v>
       </c>
       <c r="D49" t="n">
-        <v>0.3023</v>
+        <v>0.2592</v>
       </c>
       <c r="E49" t="n">
-        <v>1.7914</v>
+        <v>1.7648</v>
       </c>
       <c r="F49" t="n">
-        <v>1.7914</v>
+        <v>1.7648</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1.7914</v>
+        <v>1.7648</v>
       </c>
       <c r="I49" t="n">
         <v>1.825</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.6959</v>
+        <v>1.6521</v>
       </c>
       <c r="C50" t="n">
-        <v>1.1411</v>
+        <v>1.1117</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2637</v>
+        <v>0.2143</v>
       </c>
       <c r="E50" t="n">
-        <v>1.6959</v>
+        <v>1.6521</v>
       </c>
       <c r="F50" t="n">
-        <v>1.6959</v>
+        <v>1.6521</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.6959</v>
+        <v>1.6521</v>
       </c>
       <c r="I50" t="n">
         <v>1.7519</v>
@@ -2750,25 +2750,25 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.6605</v>
+        <v>1.6115</v>
       </c>
       <c r="C51" t="n">
-        <v>1.1173</v>
+        <v>1.0843</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2494</v>
+        <v>0.1981</v>
       </c>
       <c r="E51" t="n">
-        <v>1.6605</v>
+        <v>1.6115</v>
       </c>
       <c r="F51" t="n">
-        <v>1.6605</v>
+        <v>1.6115</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.6605</v>
+        <v>1.6115</v>
       </c>
       <c r="I51" t="n">
         <v>1.7233</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.6591</v>
+        <v>1.5923</v>
       </c>
       <c r="C52" t="n">
-        <v>1.1164</v>
+        <v>1.0714</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2489</v>
+        <v>0.1905</v>
       </c>
       <c r="E52" t="n">
-        <v>1.6591</v>
+        <v>1.5923</v>
       </c>
       <c r="F52" t="n">
-        <v>1.6591</v>
+        <v>1.5923</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.6591</v>
+        <v>1.5923</v>
       </c>
       <c r="I52" t="n">
         <v>1.7461</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.5117</v>
+        <v>1.4726</v>
       </c>
       <c r="C53" t="n">
-        <v>1.0172</v>
+        <v>0.9909</v>
       </c>
       <c r="D53" t="n">
-        <v>0.1893</v>
+        <v>0.1428</v>
       </c>
       <c r="E53" t="n">
-        <v>1.5117</v>
+        <v>1.4726</v>
       </c>
       <c r="F53" t="n">
-        <v>1.5117</v>
+        <v>1.4726</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1.5117</v>
+        <v>1.4726</v>
       </c>
       <c r="I53" t="n">
         <v>1.5616</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.5066</v>
+        <v>1.4677</v>
       </c>
       <c r="C54" t="n">
-        <v>1.0137</v>
+        <v>0.9876</v>
       </c>
       <c r="D54" t="n">
-        <v>0.1873</v>
+        <v>0.1408</v>
       </c>
       <c r="E54" t="n">
-        <v>1.5066</v>
+        <v>1.4677</v>
       </c>
       <c r="F54" t="n">
-        <v>1.5066</v>
+        <v>1.4677</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1.5066</v>
+        <v>1.4677</v>
       </c>
       <c r="I54" t="n">
         <v>1.5564</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.4485</v>
+        <v>1.4164</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9747</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>0.1638</v>
+        <v>0.1204</v>
       </c>
       <c r="E55" t="n">
-        <v>1.4485</v>
+        <v>1.4164</v>
       </c>
       <c r="F55" t="n">
-        <v>1.4485</v>
+        <v>1.4164</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1.4485</v>
+        <v>1.4164</v>
       </c>
       <c r="I55" t="n">
         <v>1.4894</v>
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.4025</v>
+        <v>1.3921</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9437</v>
+        <v>0.9367</v>
       </c>
       <c r="D56" t="n">
-        <v>0.1452</v>
+        <v>0.1107</v>
       </c>
       <c r="E56" t="n">
-        <v>1.4025</v>
+        <v>1.3921</v>
       </c>
       <c r="F56" t="n">
-        <v>1.4025</v>
+        <v>1.3921</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1.4025</v>
+        <v>1.3921</v>
       </c>
       <c r="I56" t="n">
         <v>1.4156</v>
@@ -3022,93 +3022,93 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.3271</v>
+        <v>1.3118</v>
       </c>
       <c r="C57" t="n">
-        <v>0.893</v>
+        <v>0.8827</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1148</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>1.3271</v>
+        <v>1.3118</v>
       </c>
       <c r="F57" t="n">
-        <v>1.3271</v>
+        <v>1.3118</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>1.3271</v>
+        <v>1.3118</v>
       </c>
       <c r="I57" t="n">
-        <v>1.3902</v>
+        <v>1.334</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>497</v>
+        <v>280</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>1.3902</v>
+        <v>1.334</v>
       </c>
       <c r="N57" t="n">
-        <v>497</v>
+        <v>280</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.3217</v>
+        <v>1.2784</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8893</v>
+        <v>0.8602</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1126</v>
+        <v>0.0654</v>
       </c>
       <c r="E58" t="n">
-        <v>1.3217</v>
+        <v>1.2784</v>
       </c>
       <c r="F58" t="n">
-        <v>1.3217</v>
+        <v>1.2784</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1.3217</v>
+        <v>1.2784</v>
       </c>
       <c r="I58" t="n">
-        <v>1.334</v>
+        <v>1.3902</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>280</v>
+        <v>497</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>1.334</v>
+        <v>1.3902</v>
       </c>
       <c r="N58" t="n">
-        <v>280</v>
+        <v>497</v>
       </c>
     </row>
     <row r="59">
@@ -3118,25 +3118,25 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.2663</v>
+        <v>1.2428</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8521</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>0.0902</v>
+        <v>0.0512</v>
       </c>
       <c r="E59" t="n">
-        <v>1.2663</v>
+        <v>1.2428</v>
       </c>
       <c r="F59" t="n">
-        <v>1.2663</v>
+        <v>1.2428</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.2663</v>
+        <v>1.2428</v>
       </c>
       <c r="I59" t="n">
         <v>1.296</v>
@@ -3164,25 +3164,25 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.2543</v>
+        <v>1.2311</v>
       </c>
       <c r="C60" t="n">
-        <v>0.844</v>
+        <v>0.8284</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0853</v>
+        <v>0.0466</v>
       </c>
       <c r="E60" t="n">
-        <v>1.2543</v>
+        <v>1.2311</v>
       </c>
       <c r="F60" t="n">
-        <v>1.2543</v>
+        <v>1.2311</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>1.2543</v>
+        <v>1.2311</v>
       </c>
       <c r="I60" t="n">
         <v>1.2837</v>
@@ -3206,93 +3206,93 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>oBo</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.1903</v>
+        <v>1.1624</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.7821</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0595</v>
+        <v>0.0192</v>
       </c>
       <c r="E61" t="n">
-        <v>1.1903</v>
+        <v>1.1624</v>
       </c>
       <c r="F61" t="n">
-        <v>1.1903</v>
+        <v>1.1624</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>1.1903</v>
+        <v>1.1624</v>
       </c>
       <c r="I61" t="n">
-        <v>1.2353</v>
+        <v>1.202</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1.2353</v>
+        <v>1.202</v>
       </c>
       <c r="N61" t="n">
-        <v>381</v>
+        <v>361</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>oBo</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.1799</v>
+        <v>1.1552</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.7773</v>
       </c>
       <c r="D62" t="n">
-        <v>0.0553</v>
+        <v>0.0163</v>
       </c>
       <c r="E62" t="n">
-        <v>1.1799</v>
+        <v>1.1552</v>
       </c>
       <c r="F62" t="n">
-        <v>1.1799</v>
+        <v>1.1552</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1.1799</v>
+        <v>1.1552</v>
       </c>
       <c r="I62" t="n">
-        <v>1.202</v>
+        <v>1.2353</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1.202</v>
+        <v>1.2353</v>
       </c>
       <c r="N62" t="n">
-        <v>361</v>
+        <v>381</v>
       </c>
     </row>
     <row r="63">
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1.0303</v>
+        <v>1.0113</v>
       </c>
       <c r="C63" t="n">
-        <v>0.6933</v>
+        <v>0.6805</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.0051</v>
+        <v>-0.041</v>
       </c>
       <c r="E63" t="n">
-        <v>1.0303</v>
+        <v>1.0113</v>
       </c>
       <c r="F63" t="n">
-        <v>1.0303</v>
+        <v>1.0113</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1.0303</v>
+        <v>1.0113</v>
       </c>
       <c r="I63" t="n">
         <v>1.0545</v>
@@ -3348,25 +3348,25 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1.0249</v>
+        <v>1.0097</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6896</v>
+        <v>0.6794</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.0073</v>
+        <v>-0.0416</v>
       </c>
       <c r="E64" t="n">
-        <v>1.0249</v>
+        <v>1.0097</v>
       </c>
       <c r="F64" t="n">
-        <v>1.0249</v>
+        <v>1.0097</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>1.0249</v>
+        <v>1.0097</v>
       </c>
       <c r="I64" t="n">
         <v>1.0442</v>
@@ -3394,25 +3394,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9468</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6515</v>
+        <v>0.6371</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.0302</v>
+        <v>-0.0667</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9468</v>
       </c>
       <c r="F65" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9468</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9468</v>
       </c>
       <c r="I65" t="n">
         <v>0.9956</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.9204</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6193</v>
+        <v>0.6034</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.0495</v>
+        <v>-0.0867</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9204</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="F66" t="n">
-        <v>0.9204</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>0.9204</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="I66" t="n">
         <v>0.9508</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.9046</v>
+        <v>0.8878</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6087</v>
+        <v>0.5974</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.0559</v>
+        <v>-0.0902</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9046</v>
+        <v>0.8878</v>
       </c>
       <c r="F67" t="n">
-        <v>0.9046</v>
+        <v>0.8878</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.9046</v>
+        <v>0.8878</v>
       </c>
       <c r="I67" t="n">
         <v>0.9258</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5352</v>
+        <v>0.5252</v>
       </c>
       <c r="C68" t="n">
-        <v>0.3601</v>
+        <v>0.3534</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.2052</v>
+        <v>-0.2347</v>
       </c>
       <c r="E68" t="n">
-        <v>0.5352</v>
+        <v>0.5252</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5352</v>
+        <v>0.5252</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.5352</v>
+        <v>0.5252</v>
       </c>
       <c r="I68" t="n">
         <v>0.5477</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.3621</v>
+        <v>0.3502</v>
       </c>
       <c r="C69" t="n">
-        <v>0.2436</v>
+        <v>0.2356</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.2751</v>
+        <v>-0.3044</v>
       </c>
       <c r="E69" t="n">
-        <v>0.3621</v>
+        <v>0.3502</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3621</v>
+        <v>0.3502</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3621</v>
+        <v>0.3502</v>
       </c>
       <c r="I69" t="n">
         <v>0.3776</v>
@@ -3624,25 +3624,25 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.3482</v>
+        <v>0.3417</v>
       </c>
       <c r="C70" t="n">
-        <v>0.2343</v>
+        <v>0.2299</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.2807</v>
+        <v>-0.3078</v>
       </c>
       <c r="E70" t="n">
-        <v>0.3482</v>
+        <v>0.3417</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3482</v>
+        <v>0.3417</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3482</v>
+        <v>0.3417</v>
       </c>
       <c r="I70" t="n">
         <v>0.3564</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.3397</v>
+        <v>0.3347</v>
       </c>
       <c r="C71" t="n">
-        <v>0.2286</v>
+        <v>0.2252</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.2841</v>
+        <v>-0.3106</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3397</v>
+        <v>0.3347</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3397</v>
+        <v>0.3347</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0.3397</v>
+        <v>0.3347</v>
       </c>
       <c r="I71" t="n">
         <v>0.3461</v>
@@ -3716,25 +3716,25 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.3019</v>
+        <v>0.2952</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2031</v>
+        <v>0.1986</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.2994</v>
+        <v>-0.3263</v>
       </c>
       <c r="E72" t="n">
-        <v>0.3019</v>
+        <v>0.2952</v>
       </c>
       <c r="F72" t="n">
-        <v>0.3019</v>
+        <v>0.2952</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0.3019</v>
+        <v>0.2952</v>
       </c>
       <c r="I72" t="n">
         <v>0.3104</v>
@@ -3762,25 +3762,25 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.1951</v>
+        <v>0.1901</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1313</v>
+        <v>0.1279</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.3425</v>
+        <v>-0.3682</v>
       </c>
       <c r="E73" t="n">
-        <v>0.1951</v>
+        <v>0.1901</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1951</v>
+        <v>0.1901</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1951</v>
+        <v>0.1901</v>
       </c>
       <c r="I73" t="n">
         <v>0.2016</v>
@@ -3808,25 +3808,25 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.0788</v>
+        <v>0.074</v>
       </c>
       <c r="C74" t="n">
-        <v>0.053</v>
+        <v>0.0498</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.3895</v>
+        <v>-0.4144</v>
       </c>
       <c r="E74" t="n">
-        <v>0.0788</v>
+        <v>0.074</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0788</v>
+        <v>0.074</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.0788</v>
+        <v>0.074</v>
       </c>
       <c r="I74" t="n">
         <v>0.0853</v>
@@ -3854,25 +3854,25 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0437</v>
+        <v>0.0431</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.3951</v>
+        <v>-0.4184</v>
       </c>
       <c r="E75" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
       <c r="F75" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0.065</v>
+        <v>0.064</v>
       </c>
       <c r="I75" t="n">
         <v>0.06619999999999999</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.0163</v>
+        <v>-0.0158</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.011</v>
+        <v>-0.0106</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.4279</v>
+        <v>-0.4502</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.0163</v>
+        <v>-0.0158</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.0163</v>
+        <v>-0.0158</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.0163</v>
+        <v>-0.0158</v>
       </c>
       <c r="I76" t="n">
         <v>-0.0169</v>
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-0.1112</v>
+        <v>-0.1087</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.07480000000000001</v>
+        <v>-0.0731</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.4663</v>
+        <v>-0.4872</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.1112</v>
+        <v>-0.1087</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.1112</v>
+        <v>-0.1087</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.1112</v>
+        <v>-0.1087</v>
       </c>
       <c r="I77" t="n">
         <v>-0.1143</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-0.2035</v>
+        <v>-0.1997</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.1369</v>
+        <v>-0.1344</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.5036</v>
+        <v>-0.5235</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.2035</v>
+        <v>-0.1997</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.2035</v>
+        <v>-0.1997</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.2035</v>
+        <v>-0.1997</v>
       </c>
       <c r="I78" t="n">
         <v>-0.2083</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-0.2136</v>
+        <v>-0.2073</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.1437</v>
+        <v>-0.1395</v>
       </c>
       <c r="D79" t="n">
-        <v>-0.5077</v>
+        <v>-0.5265</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.2136</v>
+        <v>-0.2073</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.2136</v>
+        <v>-0.2073</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.2136</v>
+        <v>-0.2073</v>
       </c>
       <c r="I79" t="n">
         <v>-0.2216</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-0.2254</v>
+        <v>-0.2179</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.1517</v>
+        <v>-0.1466</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.5124</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.2254</v>
+        <v>-0.2179</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.2254</v>
+        <v>-0.2179</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.2254</v>
+        <v>-0.2179</v>
       </c>
       <c r="I80" t="n">
         <v>-0.235</v>
@@ -4130,25 +4130,25 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-0.2715</v>
+        <v>-0.2705</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.1827</v>
+        <v>-0.182</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.531</v>
+        <v>-0.5517</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.2715</v>
+        <v>-0.2705</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.2715</v>
+        <v>-0.2705</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.2715</v>
+        <v>-0.2705</v>
       </c>
       <c r="I81" t="n">
         <v>-0.2728</v>
@@ -4176,25 +4176,25 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-0.3984</v>
+        <v>-0.3954</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.2681</v>
+        <v>-0.2661</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.5823</v>
+        <v>-0.6014</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.3984</v>
+        <v>-0.3954</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.3984</v>
+        <v>-0.3954</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.3984</v>
+        <v>-0.3954</v>
       </c>
       <c r="I82" t="n">
         <v>-0.4021</v>
@@ -4222,25 +4222,25 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>-0.521</v>
+        <v>-0.5172</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.3506</v>
+        <v>-0.348</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.6318</v>
+        <v>-0.65</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.521</v>
+        <v>-0.5172</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.521</v>
+        <v>-0.5172</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.521</v>
+        <v>-0.5172</v>
       </c>
       <c r="I83" t="n">
         <v>-0.5259</v>
@@ -4268,25 +4268,25 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>-0.6223</v>
+        <v>-0.5972</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.4187</v>
+        <v>-0.4018</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.6728</v>
+        <v>-0.6818</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.6223</v>
+        <v>-0.5972</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.6223</v>
+        <v>-0.5972</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.6223</v>
+        <v>-0.5972</v>
       </c>
       <c r="I84" t="n">
         <v>-0.6549</v>
@@ -4314,25 +4314,25 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.7211</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.5036</v>
+        <v>-0.4852</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.7237</v>
+        <v>-0.7312</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.7211</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.7211</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-0.7211</v>
       </c>
       <c r="I85" t="n">
         <v>-0.7841</v>
@@ -4360,25 +4360,25 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.8846000000000001</v>
+        <v>-0.878</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.5952</v>
+        <v>-0.5908</v>
       </c>
       <c r="D86" t="n">
-        <v>-0.7786999999999999</v>
+        <v>-0.7937</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.8846000000000001</v>
+        <v>-0.878</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.8846000000000001</v>
+        <v>-0.878</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.8846000000000001</v>
+        <v>-0.878</v>
       </c>
       <c r="I86" t="n">
         <v>-0.8929</v>
@@ -4406,25 +4406,25 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.9089</v>
+        <v>-0.8855</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.6116</v>
+        <v>-0.5958</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.7885</v>
+        <v>-0.7967</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.9089</v>
+        <v>-0.8855</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.9089</v>
+        <v>-0.8855</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.9089</v>
+        <v>-0.8855</v>
       </c>
       <c r="I87" t="n">
         <v>-0.9389999999999999</v>
@@ -4452,25 +4452,25 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-0.9268</v>
+        <v>-0.8895</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.6236</v>
+        <v>-0.5985</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.7958</v>
+        <v>-0.7983</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.9268</v>
+        <v>-0.8895</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.9268</v>
+        <v>-0.8895</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.9268</v>
+        <v>-0.8895</v>
       </c>
       <c r="I88" t="n">
         <v>-0.9754</v>
@@ -4498,25 +4498,25 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-0.9549</v>
+        <v>-0.9029</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.6425</v>
+        <v>-0.6075</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.8071</v>
+        <v>-0.8036</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.9549</v>
+        <v>-0.9029</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.9549</v>
+        <v>-0.9029</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.9549</v>
+        <v>-0.9029</v>
       </c>
       <c r="I89" t="n">
         <v>-1.0238</v>
@@ -4544,25 +4544,25 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>-0.9961</v>
+        <v>-0.9813</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.6702</v>
+        <v>-0.6603</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.8238</v>
+        <v>-0.8349</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.9961</v>
+        <v>-0.9813</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.9961</v>
+        <v>-0.9813</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.9961</v>
+        <v>-0.9813</v>
       </c>
       <c r="I90" t="n">
         <v>-1.0148</v>
@@ -4590,25 +4590,25 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-1.1045</v>
+        <v>-1.084</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.7432</v>
+        <v>-0.7294</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.8676</v>
+        <v>-0.8758</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.1045</v>
+        <v>-1.084</v>
       </c>
       <c r="F91" t="n">
-        <v>-1.1045</v>
+        <v>-1.084</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>-1.1045</v>
+        <v>-1.084</v>
       </c>
       <c r="I91" t="n">
         <v>-1.1304</v>
@@ -4636,25 +4636,25 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-1.1323</v>
+        <v>-1.099</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.7619</v>
+        <v>-0.7395</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.8788</v>
+        <v>-0.8818</v>
       </c>
       <c r="E92" t="n">
-        <v>-1.1323</v>
+        <v>-1.099</v>
       </c>
       <c r="F92" t="n">
-        <v>-1.1323</v>
+        <v>-1.099</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-1.1323</v>
+        <v>-1.099</v>
       </c>
       <c r="I92" t="n">
         <v>-1.1752</v>
@@ -4682,25 +4682,25 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>-1.3129</v>
+        <v>-1.2647</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.8834</v>
+        <v>-0.851</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.9517</v>
+        <v>-0.9478</v>
       </c>
       <c r="E93" t="n">
-        <v>-1.3129</v>
+        <v>-1.2647</v>
       </c>
       <c r="F93" t="n">
-        <v>-1.3129</v>
+        <v>-1.2647</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>-1.3129</v>
+        <v>-1.2647</v>
       </c>
       <c r="I93" t="n">
         <v>-1.3753</v>
@@ -4728,25 +4728,25 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-1.4598</v>
+        <v>-1.4382</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.9823</v>
+        <v>-0.9677</v>
       </c>
       <c r="D94" t="n">
-        <v>-1.0111</v>
+        <v>-1.0169</v>
       </c>
       <c r="E94" t="n">
-        <v>-1.4598</v>
+        <v>-1.4382</v>
       </c>
       <c r="F94" t="n">
-        <v>-1.4598</v>
+        <v>-1.4382</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>-1.4598</v>
+        <v>-1.4382</v>
       </c>
       <c r="I94" t="n">
         <v>-1.4872</v>
@@ -4770,185 +4770,185 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>malta</t>
+          <t>Grim</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-1.5233</v>
+        <v>-1.4806</v>
       </c>
       <c r="C95" t="n">
-        <v>-1.025</v>
+        <v>-0.9963</v>
       </c>
       <c r="D95" t="n">
-        <v>-1.0367</v>
+        <v>-1.0338</v>
       </c>
       <c r="E95" t="n">
-        <v>-1.5233</v>
+        <v>-1.4806</v>
       </c>
       <c r="F95" t="n">
-        <v>-1.5233</v>
+        <v>-1.4806</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>-1.5233</v>
+        <v>-1.4806</v>
       </c>
       <c r="I95" t="n">
-        <v>-1.5375</v>
+        <v>-1.5966</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>275</v>
+        <v>369</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>-1.5375</v>
+        <v>-1.5966</v>
       </c>
       <c r="N95" t="n">
-        <v>275</v>
+        <v>369</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Grim</t>
+          <t>malta</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-1.5312</v>
+        <v>-1.5119</v>
       </c>
       <c r="C96" t="n">
-        <v>-1.0303</v>
+        <v>-1.0173</v>
       </c>
       <c r="D96" t="n">
-        <v>-1.0399</v>
+        <v>-1.0463</v>
       </c>
       <c r="E96" t="n">
-        <v>-1.5312</v>
+        <v>-1.5119</v>
       </c>
       <c r="F96" t="n">
-        <v>-1.5312</v>
+        <v>-1.5119</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>-1.5312</v>
+        <v>-1.5119</v>
       </c>
       <c r="I96" t="n">
-        <v>-1.5966</v>
+        <v>-1.5375</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>369</v>
+        <v>275</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>-1.5966</v>
+        <v>-1.5375</v>
       </c>
       <c r="N96" t="n">
-        <v>369</v>
+        <v>275</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-1.6102</v>
+        <v>-1.5761</v>
       </c>
       <c r="C97" t="n">
-        <v>-1.0835</v>
+        <v>-1.0605</v>
       </c>
       <c r="D97" t="n">
         <v>-1.0718</v>
       </c>
       <c r="E97" t="n">
-        <v>-1.6102</v>
+        <v>-1.5761</v>
       </c>
       <c r="F97" t="n">
-        <v>-1.6102</v>
+        <v>-1.5761</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>-1.6102</v>
+        <v>-1.5761</v>
       </c>
       <c r="I97" t="n">
-        <v>-1.6404</v>
+        <v>-1.6996</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>282</v>
+        <v>446</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>-1.6404</v>
+        <v>-1.6996</v>
       </c>
       <c r="N97" t="n">
-        <v>282</v>
+        <v>446</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-1.63</v>
+        <v>-1.5863</v>
       </c>
       <c r="C98" t="n">
-        <v>-1.0968</v>
+        <v>-1.0674</v>
       </c>
       <c r="D98" t="n">
-        <v>-1.0798</v>
+        <v>-1.0759</v>
       </c>
       <c r="E98" t="n">
-        <v>-1.63</v>
+        <v>-1.5863</v>
       </c>
       <c r="F98" t="n">
-        <v>-1.63</v>
+        <v>-1.5863</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>-1.63</v>
+        <v>-1.5863</v>
       </c>
       <c r="I98" t="n">
-        <v>-1.6996</v>
+        <v>-1.6404</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>446</v>
+        <v>282</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>-1.6996</v>
+        <v>-1.6404</v>
       </c>
       <c r="N98" t="n">
-        <v>446</v>
+        <v>282</v>
       </c>
     </row>
     <row r="99">
@@ -4958,25 +4958,25 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-1.6442</v>
+        <v>-1.6198</v>
       </c>
       <c r="C99" t="n">
-        <v>-1.1063</v>
+        <v>-1.0899</v>
       </c>
       <c r="D99" t="n">
-        <v>-1.0856</v>
+        <v>-1.0892</v>
       </c>
       <c r="E99" t="n">
-        <v>-1.6442</v>
+        <v>-1.6198</v>
       </c>
       <c r="F99" t="n">
-        <v>-1.6442</v>
+        <v>-1.6198</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.6442</v>
+        <v>-1.6198</v>
       </c>
       <c r="I99" t="n">
         <v>-1.675</v>
@@ -5004,25 +5004,25 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-1.7199</v>
+        <v>-1.663</v>
       </c>
       <c r="C100" t="n">
-        <v>-1.1573</v>
+        <v>-1.119</v>
       </c>
       <c r="D100" t="n">
-        <v>-1.1162</v>
+        <v>-1.1064</v>
       </c>
       <c r="E100" t="n">
-        <v>-1.7199</v>
+        <v>-1.663</v>
       </c>
       <c r="F100" t="n">
-        <v>-1.7199</v>
+        <v>-1.663</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>-1.7199</v>
+        <v>-1.663</v>
       </c>
       <c r="I100" t="n">
         <v>-1.7933</v>
@@ -5046,93 +5046,93 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-1.7417</v>
+        <v>-1.7067</v>
       </c>
       <c r="C101" t="n">
-        <v>-1.1719</v>
+        <v>-1.1484</v>
       </c>
       <c r="D101" t="n">
-        <v>-1.125</v>
+        <v>-1.1239</v>
       </c>
       <c r="E101" t="n">
-        <v>-1.7417</v>
+        <v>-1.7067</v>
       </c>
       <c r="F101" t="n">
-        <v>-1.7417</v>
+        <v>-1.7067</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>-1.7417</v>
+        <v>-1.7067</v>
       </c>
       <c r="I101" t="n">
-        <v>-1.758</v>
+        <v>-1.8098</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>-1.758</v>
+        <v>-1.8098</v>
       </c>
       <c r="N101" t="n">
-        <v>311</v>
+        <v>345</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-1.7519</v>
+        <v>-1.7288</v>
       </c>
       <c r="C102" t="n">
-        <v>-1.1788</v>
+        <v>-1.1633</v>
       </c>
       <c r="D102" t="n">
-        <v>-1.1291</v>
+        <v>-1.1327</v>
       </c>
       <c r="E102" t="n">
-        <v>-1.7519</v>
+        <v>-1.7288</v>
       </c>
       <c r="F102" t="n">
-        <v>-1.7519</v>
+        <v>-1.7288</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.7519</v>
+        <v>-1.7288</v>
       </c>
       <c r="I102" t="n">
-        <v>-1.8098</v>
+        <v>-1.758</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>345</v>
+        <v>311</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>-1.8098</v>
+        <v>-1.758</v>
       </c>
       <c r="N102" t="n">
-        <v>345</v>
+        <v>311</v>
       </c>
     </row>
     <row r="103">
@@ -5142,25 +5142,25 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>-2.0008</v>
+        <v>-1.9711</v>
       </c>
       <c r="C103" t="n">
-        <v>-1.3463</v>
+        <v>-1.3263</v>
       </c>
       <c r="D103" t="n">
-        <v>-1.2296</v>
+        <v>-1.2292</v>
       </c>
       <c r="E103" t="n">
-        <v>-2.0008</v>
+        <v>-1.9711</v>
       </c>
       <c r="F103" t="n">
-        <v>-2.0008</v>
+        <v>-1.9711</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>-2.0008</v>
+        <v>-1.9711</v>
       </c>
       <c r="I103" t="n">
         <v>-2.0383</v>
@@ -5188,25 +5188,25 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-2.0399</v>
+        <v>-1.9872</v>
       </c>
       <c r="C104" t="n">
-        <v>-1.3726</v>
+        <v>-1.3371</v>
       </c>
       <c r="D104" t="n">
-        <v>-1.2454</v>
+        <v>-1.2356</v>
       </c>
       <c r="E104" t="n">
-        <v>-2.0399</v>
+        <v>-1.9872</v>
       </c>
       <c r="F104" t="n">
-        <v>-2.0399</v>
+        <v>-1.9872</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.0399</v>
+        <v>-1.9872</v>
       </c>
       <c r="I104" t="n">
         <v>-2.1073</v>
@@ -5234,25 +5234,25 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-2.0502</v>
+        <v>-1.9973</v>
       </c>
       <c r="C105" t="n">
-        <v>-1.3795</v>
+        <v>-1.3439</v>
       </c>
       <c r="D105" t="n">
-        <v>-1.2496</v>
+        <v>-1.2396</v>
       </c>
       <c r="E105" t="n">
-        <v>-2.0502</v>
+        <v>-1.9973</v>
       </c>
       <c r="F105" t="n">
-        <v>-2.0502</v>
+        <v>-1.9973</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>-2.0502</v>
+        <v>-1.9973</v>
       </c>
       <c r="I105" t="n">
         <v>-2.1179</v>
@@ -5276,93 +5276,93 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-2.12</v>
+        <v>-2.0637</v>
       </c>
       <c r="C106" t="n">
-        <v>-1.4265</v>
+        <v>-1.3886</v>
       </c>
       <c r="D106" t="n">
-        <v>-1.2778</v>
+        <v>-1.2661</v>
       </c>
       <c r="E106" t="n">
-        <v>-2.12</v>
+        <v>-2.0637</v>
       </c>
       <c r="F106" t="n">
-        <v>-2.12</v>
+        <v>-2.0637</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>-2.12</v>
+        <v>-2.0637</v>
       </c>
       <c r="I106" t="n">
-        <v>-2.1497</v>
+        <v>-2.2068</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>163</v>
+        <v>381</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>-2.1497</v>
+        <v>-2.2068</v>
       </c>
       <c r="N106" t="n">
-        <v>163</v>
+        <v>381</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-2.1263</v>
+        <v>-2.0963</v>
       </c>
       <c r="C107" t="n">
-        <v>-1.4307</v>
+        <v>-1.4105</v>
       </c>
       <c r="D107" t="n">
-        <v>-1.2803</v>
+        <v>-1.2791</v>
       </c>
       <c r="E107" t="n">
-        <v>-2.1263</v>
+        <v>-2.0963</v>
       </c>
       <c r="F107" t="n">
-        <v>-2.1263</v>
+        <v>-2.0963</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>-2.1263</v>
+        <v>-2.0963</v>
       </c>
       <c r="I107" t="n">
-        <v>-2.2068</v>
+        <v>-2.1497</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>381</v>
+        <v>163</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>-2.2068</v>
+        <v>-2.1497</v>
       </c>
       <c r="N107" t="n">
-        <v>381</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108">
@@ -5372,25 +5372,25 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-2.2516</v>
+        <v>-2.2348</v>
       </c>
       <c r="C108" t="n">
-        <v>-1.515</v>
+        <v>-1.5037</v>
       </c>
       <c r="D108" t="n">
-        <v>-1.331</v>
+        <v>-1.3343</v>
       </c>
       <c r="E108" t="n">
-        <v>-2.2516</v>
+        <v>-2.2348</v>
       </c>
       <c r="F108" t="n">
-        <v>-2.2516</v>
+        <v>-2.2348</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>-2.2516</v>
+        <v>-2.2348</v>
       </c>
       <c r="I108" t="n">
         <v>-2.2726</v>
@@ -5414,124 +5414,124 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MiGHTYMAX</t>
+          <t>doto</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-2.5108</v>
+        <v>-2.4709</v>
       </c>
       <c r="C109" t="n">
-        <v>-1.6894</v>
+        <v>-1.6626</v>
       </c>
       <c r="D109" t="n">
-        <v>-1.4357</v>
+        <v>-1.4283</v>
       </c>
       <c r="E109" t="n">
-        <v>-2.5108</v>
+        <v>-2.4709</v>
       </c>
       <c r="F109" t="n">
-        <v>-2.5108</v>
+        <v>-2.4709</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>-2.5108</v>
+        <v>-2.4709</v>
       </c>
       <c r="I109" t="n">
-        <v>-2.5579</v>
+        <v>-2.6422</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>266</v>
+        <v>381</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>-2.5579</v>
+        <v>-2.6422</v>
       </c>
       <c r="N109" t="n">
-        <v>266</v>
+        <v>381</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Hatz</t>
+          <t>MiGHTYMAX</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-2.5254</v>
+        <v>-2.4736</v>
       </c>
       <c r="C110" t="n">
-        <v>-1.6993</v>
+        <v>-1.6644</v>
       </c>
       <c r="D110" t="n">
-        <v>-1.4416</v>
+        <v>-1.4294</v>
       </c>
       <c r="E110" t="n">
-        <v>-2.5254</v>
+        <v>-2.4736</v>
       </c>
       <c r="F110" t="n">
-        <v>-2.5254</v>
+        <v>-2.4736</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>-2.5254</v>
+        <v>-2.4736</v>
       </c>
       <c r="I110" t="n">
-        <v>-2.549</v>
+        <v>-2.5579</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>-2.549</v>
+        <v>-2.5579</v>
       </c>
       <c r="N110" t="n">
-        <v>275</v>
+        <v>266</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sico</t>
+          <t>Hatz</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>-2.5394</v>
+        <v>-2.5066</v>
       </c>
       <c r="C111" t="n">
-        <v>-1.7087</v>
+        <v>-1.6866</v>
       </c>
       <c r="D111" t="n">
-        <v>-1.4472</v>
+        <v>-1.4425</v>
       </c>
       <c r="E111" t="n">
-        <v>-2.5394</v>
+        <v>-2.5066</v>
       </c>
       <c r="F111" t="n">
-        <v>-2.5394</v>
+        <v>-2.5066</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>-2.5394</v>
+        <v>-2.5066</v>
       </c>
       <c r="I111" t="n">
-        <v>-2.5631</v>
+        <v>-2.549</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>-2.5631</v>
+        <v>-2.549</v>
       </c>
       <c r="N111" t="n">
         <v>275</v>
@@ -5552,93 +5552,93 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>doto</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-2.5458</v>
+        <v>-2.508</v>
       </c>
       <c r="C112" t="n">
-        <v>-1.713</v>
+        <v>-1.6876</v>
       </c>
       <c r="D112" t="n">
-        <v>-1.4498</v>
+        <v>-1.4431</v>
       </c>
       <c r="E112" t="n">
-        <v>-2.5458</v>
+        <v>-2.508</v>
       </c>
       <c r="F112" t="n">
-        <v>-2.5458</v>
+        <v>-2.508</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>-2.5458</v>
+        <v>-2.508</v>
       </c>
       <c r="I112" t="n">
-        <v>-2.6422</v>
+        <v>-2.7045</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>381</v>
+        <v>446</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>-2.6422</v>
+        <v>-2.7045</v>
       </c>
       <c r="N112" t="n">
-        <v>381</v>
+        <v>446</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Sico</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-2.5938</v>
+        <v>-2.5205</v>
       </c>
       <c r="C113" t="n">
-        <v>-1.7453</v>
+        <v>-1.696</v>
       </c>
       <c r="D113" t="n">
-        <v>-1.4692</v>
+        <v>-1.4481</v>
       </c>
       <c r="E113" t="n">
-        <v>-2.5938</v>
+        <v>-2.5205</v>
       </c>
       <c r="F113" t="n">
-        <v>-2.5938</v>
+        <v>-2.5205</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>-2.5938</v>
+        <v>-2.5205</v>
       </c>
       <c r="I113" t="n">
-        <v>-2.7045</v>
+        <v>-2.5631</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>446</v>
+        <v>275</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>-2.7045</v>
+        <v>-2.5631</v>
       </c>
       <c r="N113" t="n">
-        <v>446</v>
+        <v>275</v>
       </c>
     </row>
     <row r="114">
@@ -5648,25 +5648,25 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-2.6659</v>
+        <v>-2.6461</v>
       </c>
       <c r="C114" t="n">
-        <v>-1.7938</v>
+        <v>-1.7805</v>
       </c>
       <c r="D114" t="n">
-        <v>-1.4983</v>
+        <v>-1.4981</v>
       </c>
       <c r="E114" t="n">
-        <v>-2.6659</v>
+        <v>-2.6461</v>
       </c>
       <c r="F114" t="n">
-        <v>-2.6659</v>
+        <v>-2.6461</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>-2.6659</v>
+        <v>-2.6461</v>
       </c>
       <c r="I114" t="n">
         <v>-2.6908</v>
@@ -5694,25 +5694,25 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-2.6971</v>
+        <v>-2.6571</v>
       </c>
       <c r="C115" t="n">
-        <v>-1.8148</v>
+        <v>-1.7879</v>
       </c>
       <c r="D115" t="n">
-        <v>-1.5109</v>
+        <v>-1.5025</v>
       </c>
       <c r="E115" t="n">
-        <v>-2.6971</v>
+        <v>-2.6571</v>
       </c>
       <c r="F115" t="n">
-        <v>-2.6971</v>
+        <v>-2.6571</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>-2.6971</v>
+        <v>-2.6571</v>
       </c>
       <c r="I115" t="n">
         <v>-2.7477</v>
@@ -5736,93 +5736,93 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>-2.7283</v>
+        <v>-2.6845</v>
       </c>
       <c r="C116" t="n">
-        <v>-1.8358</v>
+        <v>-1.8063</v>
       </c>
       <c r="D116" t="n">
-        <v>-1.5235</v>
+        <v>-1.5134</v>
       </c>
       <c r="E116" t="n">
-        <v>-2.7283</v>
+        <v>-2.6845</v>
       </c>
       <c r="F116" t="n">
-        <v>-2.7283</v>
+        <v>-2.6845</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>-2.7283</v>
+        <v>-2.6845</v>
       </c>
       <c r="I116" t="n">
-        <v>-2.7794</v>
+        <v>-2.8467</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>-2.7794</v>
+        <v>-2.8467</v>
       </c>
       <c r="N116" t="n">
-        <v>282</v>
+        <v>358</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-2.7557</v>
+        <v>-2.6878</v>
       </c>
       <c r="C117" t="n">
-        <v>-1.8542</v>
+        <v>-1.8085</v>
       </c>
       <c r="D117" t="n">
-        <v>-1.5346</v>
+        <v>-1.5147</v>
       </c>
       <c r="E117" t="n">
-        <v>-2.7557</v>
+        <v>-2.6878</v>
       </c>
       <c r="F117" t="n">
-        <v>-2.7557</v>
+        <v>-2.6878</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>-2.7557</v>
+        <v>-2.6878</v>
       </c>
       <c r="I117" t="n">
-        <v>-2.8467</v>
+        <v>-2.7794</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>358</v>
+        <v>282</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>-2.8467</v>
+        <v>-2.7794</v>
       </c>
       <c r="N117" t="n">
-        <v>358</v>
+        <v>282</v>
       </c>
     </row>
     <row r="118">
@@ -5832,25 +5832,25 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-2.8102</v>
+        <v>-2.7893</v>
       </c>
       <c r="C118" t="n">
-        <v>-1.8909</v>
+        <v>-1.8768</v>
       </c>
       <c r="D118" t="n">
-        <v>-1.5566</v>
+        <v>-1.5552</v>
       </c>
       <c r="E118" t="n">
-        <v>-2.8102</v>
+        <v>-2.7893</v>
       </c>
       <c r="F118" t="n">
-        <v>-2.8102</v>
+        <v>-2.7893</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>-2.8102</v>
+        <v>-2.7893</v>
       </c>
       <c r="I118" t="n">
         <v>-2.8364</v>
@@ -5878,25 +5878,25 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-2.8516</v>
+        <v>-2.7988</v>
       </c>
       <c r="C119" t="n">
-        <v>-1.9188</v>
+        <v>-1.8832</v>
       </c>
       <c r="D119" t="n">
-        <v>-1.5733</v>
+        <v>-1.559</v>
       </c>
       <c r="E119" t="n">
-        <v>-2.8516</v>
+        <v>-2.7988</v>
       </c>
       <c r="F119" t="n">
-        <v>-2.8516</v>
+        <v>-2.7988</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>-2.8516</v>
+        <v>-2.7988</v>
       </c>
       <c r="I119" t="n">
         <v>-2.9186</v>
@@ -5924,25 +5924,25 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-3.5148</v>
+        <v>-3.3859</v>
       </c>
       <c r="C120" t="n">
-        <v>-2.365</v>
+        <v>-2.2783</v>
       </c>
       <c r="D120" t="n">
-        <v>-1.8413</v>
+        <v>-1.7929</v>
       </c>
       <c r="E120" t="n">
-        <v>-3.5148</v>
+        <v>-3.3859</v>
       </c>
       <c r="F120" t="n">
-        <v>-3.5148</v>
+        <v>-3.3859</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>-3.5148</v>
+        <v>-3.3859</v>
       </c>
       <c r="I120" t="n">
         <v>-3.6819</v>
@@ -5970,25 +5970,25 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-3.6281</v>
+        <v>-3.6011</v>
       </c>
       <c r="C121" t="n">
-        <v>-2.4412</v>
+        <v>-2.4231</v>
       </c>
       <c r="D121" t="n">
-        <v>-1.887</v>
+        <v>-1.8786</v>
       </c>
       <c r="E121" t="n">
-        <v>-3.6281</v>
+        <v>-3.6011</v>
       </c>
       <c r="F121" t="n">
-        <v>-3.6281</v>
+        <v>-3.6011</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>-3.6281</v>
+        <v>-3.6011</v>
       </c>
       <c r="I121" t="n">
         <v>-3.662</v>
@@ -6016,25 +6016,25 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-3.9314</v>
+        <v>-3.9021</v>
       </c>
       <c r="C122" t="n">
-        <v>-2.6453</v>
+        <v>-2.6256</v>
       </c>
       <c r="D122" t="n">
-        <v>-2.0096</v>
+        <v>-1.9985</v>
       </c>
       <c r="E122" t="n">
-        <v>-3.9314</v>
+        <v>-3.9021</v>
       </c>
       <c r="F122" t="n">
-        <v>-3.9314</v>
+        <v>-3.9021</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>-3.9314</v>
+        <v>-3.9021</v>
       </c>
       <c r="I122" t="n">
         <v>-3.9681</v>
@@ -6062,25 +6062,25 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-7.3654</v>
+        <v>-7.0952</v>
       </c>
       <c r="C123" t="n">
-        <v>-4.956</v>
+        <v>-4.7742</v>
       </c>
       <c r="D123" t="n">
-        <v>-3.3968</v>
+        <v>-3.2706</v>
       </c>
       <c r="E123" t="n">
-        <v>-7.3654</v>
+        <v>-7.0952</v>
       </c>
       <c r="F123" t="n">
-        <v>-7.3654</v>
+        <v>-7.0952</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>-7.3654</v>
+        <v>-7.0952</v>
       </c>
       <c r="I123" t="n">
         <v>-7.7155</v>
